--- a/tests/fixtures/master_import/候选人面试安排管理列表_test.xlsx
+++ b/tests/fixtures/master_import/候选人面试安排管理列表_test.xlsx
@@ -476,12 +476,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SR20260101001</t>
+          <t>SR2026010100001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SR20260101001</t>
+          <t>SR2026010100001</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -529,12 +529,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SR20260102002</t>
+          <t>SR2026010200002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SR20260102002</t>
+          <t>SR2026010200002</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">

--- a/tests/fixtures/master_import/候选人面试安排管理列表_test.xlsx
+++ b/tests/fixtures/master_import/候选人面试安排管理列表_test.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -570,6 +570,296 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SR2026020500005</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SR2026020500005</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>状态05笔试</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>+86 XXXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>笔试</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SR2026020600006</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SR2026020600006</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>状态06性格测评</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>+86 XXXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>性格测评</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SR2026020700007</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SR2026020700007</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>状态07资格面试</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>+86 XXXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>资格面试</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>考核中</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SR2026020800008</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SR2026020800008</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>状态08技术面</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>+86 XXXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>技术面</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>考核中</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SR2026020900009</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SR2026020900009</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>状态09主管面</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>+86 XXXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>主管面</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>考核中</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SR2026021000010</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SR2026021000010</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>状态10offer策略</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>+86 XXXXXXXXXXX</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>报批</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>考核中</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
